--- a/data/nzd0088/nzd0088.xlsx
+++ b/data/nzd0088/nzd0088.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F314"/>
+  <dimension ref="A1:F315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7970,6 +7970,30 @@
       <c r="F314" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>351.91</v>
+      </c>
+      <c r="C315" t="n">
+        <v>348.64</v>
+      </c>
+      <c r="D315" t="n">
+        <v>349.1</v>
+      </c>
+      <c r="E315" t="n">
+        <v>352.01</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -7984,7 +8008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B323"/>
+  <dimension ref="A1:B324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11217,6 +11241,16 @@
       </c>
       <c r="B323" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -11385,28 +11419,28 @@
         <v>0.08459999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07873276308961163</v>
+        <v>0.07912323040453884</v>
       </c>
       <c r="J2" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K2" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01620755002494889</v>
+        <v>0.01648051554928232</v>
       </c>
       <c r="M2" t="n">
-        <v>3.282809325970967</v>
+        <v>3.274120768948238</v>
       </c>
       <c r="N2" t="n">
-        <v>19.21087703314693</v>
+        <v>19.15078627606803</v>
       </c>
       <c r="O2" t="n">
-        <v>4.383021450226651</v>
+        <v>4.376161134609651</v>
       </c>
       <c r="P2" t="n">
-        <v>349.2556233621391</v>
+        <v>349.2514401336991</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11463,28 +11497,28 @@
         <v>0.0854</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1946124910405271</v>
+        <v>0.1931465728828172</v>
       </c>
       <c r="J3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L3" t="n">
-        <v>0.070795239015497</v>
+        <v>0.07023240205267489</v>
       </c>
       <c r="M3" t="n">
-        <v>3.625507925133503</v>
+        <v>3.621196211306331</v>
       </c>
       <c r="N3" t="n">
-        <v>25.38042491786665</v>
+        <v>25.31496391387342</v>
       </c>
       <c r="O3" t="n">
-        <v>5.03789885943204</v>
+        <v>5.031397809145429</v>
       </c>
       <c r="P3" t="n">
-        <v>345.7475965485566</v>
+        <v>345.7633015007859</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11541,28 +11575,28 @@
         <v>0.0801</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2173216571285147</v>
+        <v>0.2145494169531421</v>
       </c>
       <c r="J4" t="n">
+        <v>314</v>
+      </c>
+      <c r="K4" t="n">
         <v>313</v>
       </c>
-      <c r="K4" t="n">
-        <v>312</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1371418192729557</v>
+        <v>0.1345385832192616</v>
       </c>
       <c r="M4" t="n">
-        <v>2.923908731592674</v>
+        <v>2.928270622619805</v>
       </c>
       <c r="N4" t="n">
-        <v>15.18390442156068</v>
+        <v>15.1904730955479</v>
       </c>
       <c r="O4" t="n">
-        <v>3.896652976794403</v>
+        <v>3.897495746700425</v>
       </c>
       <c r="P4" t="n">
-        <v>347.5849824451844</v>
+        <v>347.6147019421766</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11619,28 +11653,28 @@
         <v>0.0842</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2671951288933959</v>
+        <v>0.2631927089937344</v>
       </c>
       <c r="J5" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K5" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1582687952088898</v>
+        <v>0.1544495048349254</v>
       </c>
       <c r="M5" t="n">
-        <v>3.359506162217833</v>
+        <v>3.367716316889106</v>
       </c>
       <c r="N5" t="n">
-        <v>19.38586998296789</v>
+        <v>19.43869702670751</v>
       </c>
       <c r="O5" t="n">
-        <v>4.402938789373285</v>
+        <v>4.408933774361723</v>
       </c>
       <c r="P5" t="n">
-        <v>351.0423385518743</v>
+        <v>351.0852180352856</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11678,7 +11712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F314"/>
+  <dimension ref="A1:F315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21725,6 +21759,38 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>-35.550380249434184,174.4711141452939</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>-35.551112773510205,174.47127080145023</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>-35.55179640760194,174.4716302563436</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>-35.55241961265471,174.47211747893655</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0088/nzd0088.xlsx
+++ b/data/nzd0088/nzd0088.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F315"/>
+  <dimension ref="A1:F316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7992,6 +7992,30 @@
         <v>352.01</v>
       </c>
       <c r="F315" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>350.44</v>
+      </c>
+      <c r="C316" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="D316" t="n">
+        <v>349.7</v>
+      </c>
+      <c r="E316" t="n">
+        <v>353.51</v>
+      </c>
+      <c r="F316" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8008,7 +8032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B324"/>
+  <dimension ref="A1:B325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11251,6 +11275,16 @@
       </c>
       <c r="B324" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -11419,28 +11453,28 @@
         <v>0.08459999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07912323040453884</v>
+        <v>0.07852964648182255</v>
       </c>
       <c r="J2" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K2" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01648051554928232</v>
+        <v>0.0163508481603063</v>
       </c>
       <c r="M2" t="n">
-        <v>3.274120768948238</v>
+        <v>3.266702462112371</v>
       </c>
       <c r="N2" t="n">
-        <v>19.15078627606803</v>
+        <v>19.09251289699063</v>
       </c>
       <c r="O2" t="n">
-        <v>4.376161134609651</v>
+        <v>4.369498014302173</v>
       </c>
       <c r="P2" t="n">
-        <v>349.2514401336991</v>
+        <v>349.257822587147</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11497,28 +11531,28 @@
         <v>0.0854</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1931465728828172</v>
+        <v>0.1926597873632839</v>
       </c>
       <c r="J3" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K3" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07023240205267489</v>
+        <v>0.07036623412605147</v>
       </c>
       <c r="M3" t="n">
-        <v>3.621196211306331</v>
+        <v>3.612074934733065</v>
       </c>
       <c r="N3" t="n">
-        <v>25.31496391387342</v>
+        <v>25.2362955836964</v>
       </c>
       <c r="O3" t="n">
-        <v>5.031397809145429</v>
+        <v>5.023573985092327</v>
       </c>
       <c r="P3" t="n">
-        <v>345.7633015007859</v>
+        <v>345.7685356147817</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11575,28 +11609,28 @@
         <v>0.0801</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2145494169531421</v>
+        <v>0.2121906631102584</v>
       </c>
       <c r="J4" t="n">
+        <v>315</v>
+      </c>
+      <c r="K4" t="n">
         <v>314</v>
       </c>
-      <c r="K4" t="n">
-        <v>313</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1345385832192616</v>
+        <v>0.1325035812721364</v>
       </c>
       <c r="M4" t="n">
-        <v>2.928270622619805</v>
+        <v>2.93070605225983</v>
       </c>
       <c r="N4" t="n">
-        <v>15.1904730955479</v>
+        <v>15.18201498413463</v>
       </c>
       <c r="O4" t="n">
-        <v>3.897495746700425</v>
+        <v>3.896410525616446</v>
       </c>
       <c r="P4" t="n">
-        <v>347.6147019421766</v>
+        <v>347.64008114115</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11653,28 +11687,28 @@
         <v>0.0842</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2631927089937344</v>
+        <v>0.2602198321613701</v>
       </c>
       <c r="J5" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K5" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1544495048349254</v>
+        <v>0.1520079236275181</v>
       </c>
       <c r="M5" t="n">
-        <v>3.367716316889106</v>
+        <v>3.370989654931131</v>
       </c>
       <c r="N5" t="n">
-        <v>19.43869702670751</v>
+        <v>19.44026693395315</v>
       </c>
       <c r="O5" t="n">
-        <v>4.408933774361723</v>
+        <v>4.409111807830818</v>
       </c>
       <c r="P5" t="n">
-        <v>351.0852180352856</v>
+        <v>351.1171836045384</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11712,7 +11746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F315"/>
+  <dimension ref="A1:F316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21791,6 +21825,38 @@
         </is>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>-35.550383147131036,174.47109832262413</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>-35.55110871088968,174.47128611992233</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>-35.55179393617712,174.47163614354068</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>-35.55241265633472,174.47213166786855</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0088/nzd0088.xlsx
+++ b/data/nzd0088/nzd0088.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F316"/>
+  <dimension ref="A1:F318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8016,6 +8016,54 @@
         <v>353.51</v>
       </c>
       <c r="F316" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>347.77</v>
+      </c>
+      <c r="C317" t="n">
+        <v>351.21</v>
+      </c>
+      <c r="D317" t="n">
+        <v>351.58</v>
+      </c>
+      <c r="E317" t="n">
+        <v>358.16</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>347.16</v>
+      </c>
+      <c r="C318" t="n">
+        <v>350.36</v>
+      </c>
+      <c r="D318" t="n">
+        <v>348.52</v>
+      </c>
+      <c r="E318" t="n">
+        <v>351.29</v>
+      </c>
+      <c r="F318" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8032,7 +8080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B325"/>
+  <dimension ref="A1:B327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11285,6 +11333,26 @@
       </c>
       <c r="B325" t="n">
         <v>0.72</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>-0.61</v>
       </c>
     </row>
   </sheetData>
@@ -11453,28 +11521,28 @@
         <v>0.08459999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07852964648182255</v>
+        <v>0.07339006334631003</v>
       </c>
       <c r="J2" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K2" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0163508481603063</v>
+        <v>0.01444865073181711</v>
       </c>
       <c r="M2" t="n">
-        <v>3.266702462112371</v>
+        <v>3.271591831866896</v>
       </c>
       <c r="N2" t="n">
-        <v>19.09251289699063</v>
+        <v>19.06536607909303</v>
       </c>
       <c r="O2" t="n">
-        <v>4.369498014302173</v>
+        <v>4.36639050922991</v>
       </c>
       <c r="P2" t="n">
-        <v>349.257822587147</v>
+        <v>349.3136298008129</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11531,28 +11599,28 @@
         <v>0.0854</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1926597873632839</v>
+        <v>0.1925310322311915</v>
       </c>
       <c r="J3" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K3" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07036623412605147</v>
+        <v>0.07124022531128338</v>
       </c>
       <c r="M3" t="n">
-        <v>3.612074934733065</v>
+        <v>3.592019417890183</v>
       </c>
       <c r="N3" t="n">
-        <v>25.2362955836964</v>
+        <v>25.07830912526883</v>
       </c>
       <c r="O3" t="n">
-        <v>5.023573985092327</v>
+        <v>5.007824789793353</v>
       </c>
       <c r="P3" t="n">
-        <v>345.7685356147817</v>
+        <v>345.7699390498908</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11609,28 +11677,28 @@
         <v>0.0801</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2121906631102584</v>
+        <v>0.2079116399518333</v>
       </c>
       <c r="J4" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K4" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1325035812721364</v>
+        <v>0.1289437836990892</v>
       </c>
       <c r="M4" t="n">
-        <v>2.93070605225983</v>
+        <v>2.93351697123442</v>
       </c>
       <c r="N4" t="n">
-        <v>15.18201498413463</v>
+        <v>15.16514049730202</v>
       </c>
       <c r="O4" t="n">
-        <v>3.896410525616446</v>
+        <v>3.894244534861931</v>
       </c>
       <c r="P4" t="n">
-        <v>347.64008114115</v>
+        <v>347.6865931582109</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11687,28 +11755,28 @@
         <v>0.0842</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2602198321613701</v>
+        <v>0.2558422513979413</v>
       </c>
       <c r="J5" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K5" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1520079236275181</v>
+        <v>0.148614465719841</v>
       </c>
       <c r="M5" t="n">
-        <v>3.370989654931131</v>
+        <v>3.371602977219434</v>
       </c>
       <c r="N5" t="n">
-        <v>19.44026693395315</v>
+        <v>19.45935219595536</v>
       </c>
       <c r="O5" t="n">
-        <v>4.409111807830818</v>
+        <v>4.411275574701196</v>
       </c>
       <c r="P5" t="n">
-        <v>351.1171836045384</v>
+        <v>351.1647570573834</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11746,7 +11814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F316"/>
+  <dimension ref="A1:F318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21857,6 +21925,70 @@
         </is>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>-35.550388410289465,174.4710695834861</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>-35.55110562218377,174.47129776615685</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>-35.551786192377506,174.4716545900892</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-35.55239109173249,174.47217565354194</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>-35.550389612732936,174.47106301761505</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>-35.55110798740911,174.47128884786923</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>-35.55179879664568,174.47162456538604</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-35.55242295168771,174.47211066824832</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0088/nzd0088.xlsx
+++ b/data/nzd0088/nzd0088.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F318"/>
+  <dimension ref="A1:F321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8064,6 +8064,78 @@
         <v>351.29</v>
       </c>
       <c r="F318" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>347.39</v>
+      </c>
+      <c r="C319" t="n">
+        <v>349.78</v>
+      </c>
+      <c r="D319" t="n">
+        <v>348.42</v>
+      </c>
+      <c r="E319" t="n">
+        <v>351.32</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>346.76</v>
+      </c>
+      <c r="C320" t="n">
+        <v>348.56</v>
+      </c>
+      <c r="D320" t="n">
+        <v>347.18</v>
+      </c>
+      <c r="E320" t="n">
+        <v>350.3</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>347.06</v>
+      </c>
+      <c r="C321" t="n">
+        <v>348.61</v>
+      </c>
+      <c r="D321" t="n">
+        <v>346.45</v>
+      </c>
+      <c r="E321" t="n">
+        <v>348.17</v>
+      </c>
+      <c r="F321" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8080,7 +8152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B327"/>
+  <dimension ref="A1:B330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11353,6 +11425,36 @@
       </c>
       <c r="B327" t="n">
         <v>-0.61</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>
@@ -11521,28 +11623,28 @@
         <v>0.08459999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07339006334631003</v>
+        <v>0.06522913753989368</v>
       </c>
       <c r="J2" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K2" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01444865073181711</v>
+        <v>0.01159795276208841</v>
       </c>
       <c r="M2" t="n">
-        <v>3.271591831866896</v>
+        <v>3.28144483511732</v>
       </c>
       <c r="N2" t="n">
-        <v>19.06536607909303</v>
+        <v>19.0475379021115</v>
       </c>
       <c r="O2" t="n">
-        <v>4.36639050922991</v>
+        <v>4.36434850832418</v>
       </c>
       <c r="P2" t="n">
-        <v>349.3136298008129</v>
+        <v>349.4025253262481</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11599,28 +11701,28 @@
         <v>0.0854</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1925310322311915</v>
+        <v>0.1888166174437181</v>
       </c>
       <c r="J3" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K3" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07124022531128338</v>
+        <v>0.07000437341691301</v>
       </c>
       <c r="M3" t="n">
-        <v>3.592019417890183</v>
+        <v>3.57623396711178</v>
       </c>
       <c r="N3" t="n">
-        <v>25.07830912526883</v>
+        <v>24.87937309897235</v>
       </c>
       <c r="O3" t="n">
-        <v>5.007824789793353</v>
+        <v>4.987922723837285</v>
       </c>
       <c r="P3" t="n">
-        <v>345.7699390498908</v>
+        <v>345.8104101010308</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11677,28 +11779,28 @@
         <v>0.0801</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2079116399518333</v>
+        <v>0.1964976718194168</v>
       </c>
       <c r="J4" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K4" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1289437836990892</v>
+        <v>0.1168303646896275</v>
       </c>
       <c r="M4" t="n">
-        <v>2.93351697123442</v>
+        <v>2.965092146336753</v>
       </c>
       <c r="N4" t="n">
-        <v>15.16514049730202</v>
+        <v>15.34286637890077</v>
       </c>
       <c r="O4" t="n">
-        <v>3.894244534861931</v>
+        <v>3.916997112444784</v>
       </c>
       <c r="P4" t="n">
-        <v>347.6865931582109</v>
+        <v>347.8110261550192</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11755,28 +11857,28 @@
         <v>0.0842</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2558422513979413</v>
+        <v>0.2402147485245868</v>
       </c>
       <c r="J5" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K5" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="L5" t="n">
-        <v>0.148614465719841</v>
+        <v>0.1322954065165903</v>
       </c>
       <c r="M5" t="n">
-        <v>3.371602977219434</v>
+        <v>3.418502844976357</v>
       </c>
       <c r="N5" t="n">
-        <v>19.45935219595536</v>
+        <v>19.88061162274006</v>
       </c>
       <c r="O5" t="n">
-        <v>4.411275574701196</v>
+        <v>4.458767948967524</v>
       </c>
       <c r="P5" t="n">
-        <v>351.1647570573834</v>
+        <v>351.335005488106</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11814,7 +11916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F318"/>
+  <dimension ref="A1:F321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21989,6 +22091,102 @@
         </is>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-35.55038915935265,174.4710654932714</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>-35.55110960132723,174.47128276244914</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>-35.55179920854974,174.4716235841864</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-35.552422812561346,174.472110952027</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>-35.55039040122028,174.47105871212574</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>-35.55111299611948,174.47126996208186</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>-35.551804316159505,174.47161141731038</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-35.55242754285751,174.47210130355106</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>-35.550389809854785,174.47106194124274</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>-35.551112856988674,174.4712704866871</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>-35.551807323058235,174.47160425455198</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-35.55243742082647,174.47208115525927</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0088/nzd0088.xlsx
+++ b/data/nzd0088/nzd0088.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F321"/>
+  <dimension ref="A1:F322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8138,6 +8138,30 @@
       <c r="F321" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>346.84</v>
+      </c>
+      <c r="C322" t="n">
+        <v>347.52</v>
+      </c>
+      <c r="D322" t="n">
+        <v>345.41</v>
+      </c>
+      <c r="E322" t="n">
+        <v>348.34</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B330"/>
+  <dimension ref="A1:B331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11455,6 +11479,16 @@
       </c>
       <c r="B330" t="n">
         <v>-0.1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -11623,28 +11657,28 @@
         <v>0.08459999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06522913753989368</v>
+        <v>0.06244293721750433</v>
       </c>
       <c r="J2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01159795276208841</v>
+        <v>0.01068206688433271</v>
       </c>
       <c r="M2" t="n">
-        <v>3.28144483511732</v>
+        <v>3.285002724739352</v>
       </c>
       <c r="N2" t="n">
-        <v>19.0475379021115</v>
+        <v>19.04543666625226</v>
       </c>
       <c r="O2" t="n">
-        <v>4.36434850832418</v>
+        <v>4.364107774362621</v>
       </c>
       <c r="P2" t="n">
-        <v>349.4025253262481</v>
+        <v>349.4329896821648</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11701,28 +11735,28 @@
         <v>0.0854</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1888166174437181</v>
+        <v>0.1866647948296478</v>
       </c>
       <c r="J3" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K3" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07000437341691301</v>
+        <v>0.06889466156510782</v>
       </c>
       <c r="M3" t="n">
-        <v>3.57623396711178</v>
+        <v>3.575462323077675</v>
       </c>
       <c r="N3" t="n">
-        <v>24.87937309897235</v>
+        <v>24.83600732334952</v>
       </c>
       <c r="O3" t="n">
-        <v>4.987922723837285</v>
+        <v>4.983573750166593</v>
       </c>
       <c r="P3" t="n">
-        <v>345.8104101010308</v>
+        <v>345.8339381616149</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11779,28 +11813,28 @@
         <v>0.0801</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1964976718194168</v>
+        <v>0.1915491266724862</v>
       </c>
       <c r="J4" t="n">
+        <v>321</v>
+      </c>
+      <c r="K4" t="n">
         <v>320</v>
       </c>
-      <c r="K4" t="n">
-        <v>319</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1168303646896275</v>
+        <v>0.1112095049293416</v>
       </c>
       <c r="M4" t="n">
-        <v>2.965092146336753</v>
+        <v>2.982699935979413</v>
       </c>
       <c r="N4" t="n">
-        <v>15.34286637890077</v>
+        <v>15.47581588616331</v>
       </c>
       <c r="O4" t="n">
-        <v>3.916997112444784</v>
+        <v>3.933931352497564</v>
       </c>
       <c r="P4" t="n">
-        <v>347.8110261550192</v>
+        <v>347.8651731043991</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11857,28 +11891,28 @@
         <v>0.0842</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2402147485245868</v>
+        <v>0.234130279729737</v>
       </c>
       <c r="J5" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K5" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1322954065165903</v>
+        <v>0.1257933427727194</v>
       </c>
       <c r="M5" t="n">
-        <v>3.418502844976357</v>
+        <v>3.438525169565808</v>
       </c>
       <c r="N5" t="n">
-        <v>19.88061162274006</v>
+        <v>20.09163678670763</v>
       </c>
       <c r="O5" t="n">
-        <v>4.458767948967524</v>
+        <v>4.482369550439548</v>
       </c>
       <c r="P5" t="n">
-        <v>351.335005488106</v>
+        <v>351.4015331607361</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -11916,7 +11950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F321"/>
+  <dimension ref="A1:F322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22187,6 +22221,38 @@
         </is>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>-35.55039024352283,174.4710595732236</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>-35.55111589003971,174.47125905029247</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>-35.55181160685848,174.47159405007332</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-35.55243663244409,174.4720827633391</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
